--- a/research/traditional_assets/database/data/canada/canada_tobacco.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_tobacco.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.273</v>
+        <v>1.222</v>
       </c>
       <c r="G2">
-        <v>-0.487938596491228</v>
+        <v>-3.66268656716418</v>
       </c>
       <c r="H2">
-        <v>-0.7653508771929823</v>
+        <v>-4.008955223880597</v>
       </c>
       <c r="I2">
-        <v>-4.184210526315789</v>
+        <v>-2.908955223880597</v>
       </c>
       <c r="J2">
-        <v>-4.184210526315789</v>
+        <v>-2.908955223880597</v>
       </c>
       <c r="K2">
-        <v>-8.75</v>
+        <v>-9.514999999999999</v>
       </c>
       <c r="L2">
-        <v>-9.594298245614034</v>
+        <v>-4.733830845771144</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>35.523</v>
+        <v>14.906</v>
       </c>
       <c r="V2">
-        <v>0.5799673469387755</v>
+        <v>0.5015477792732167</v>
       </c>
       <c r="W2">
-        <v>-2.182203389830509</v>
+        <v>-1.682135706340378</v>
       </c>
       <c r="X2">
-        <v>0.04495311878408959</v>
+        <v>0.0856357406150477</v>
       </c>
       <c r="Y2">
-        <v>-2.227156508614598</v>
+        <v>-1.767771446955426</v>
       </c>
       <c r="Z2">
-        <v>1.249315068493151</v>
+        <v>0.2240303165403477</v>
       </c>
       <c r="AA2">
-        <v>-3.259574468085107</v>
+        <v>-1.092958340607362</v>
       </c>
       <c r="AB2">
-        <v>0.04462101158945921</v>
+        <v>0.08484656677678087</v>
       </c>
       <c r="AC2">
-        <v>-3.304195479674567</v>
+        <v>-1.177804907384143</v>
       </c>
       <c r="AD2">
-        <v>2.078</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.078</v>
+        <v>1.25</v>
       </c>
       <c r="AG2">
-        <v>-33.44499999999999</v>
+        <v>-13.656</v>
       </c>
       <c r="AH2">
-        <v>0.0328132895401718</v>
+        <v>0.04036164029706167</v>
       </c>
       <c r="AI2">
-        <v>0.0453039155838493</v>
+        <v>0.05748183573990619</v>
       </c>
       <c r="AJ2">
-        <v>-1.202841215608703</v>
+        <v>-0.8500996015936255</v>
       </c>
       <c r="AK2">
-        <v>-3.232962783953598</v>
+        <v>-1.996491228070176</v>
       </c>
       <c r="AL2">
-        <v>0.07300000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="AM2">
-        <v>0.03600000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AN2">
-        <v>-2.730617608409986</v>
+        <v>-0.2277281836400073</v>
       </c>
       <c r="AO2">
-        <v>-52.27397260273972</v>
+        <v>-72.18518518518518</v>
       </c>
       <c r="AP2">
-        <v>43.94875164257555</v>
+        <v>2.487884860630352</v>
       </c>
       <c r="AQ2">
-        <v>-106</v>
+        <v>-292.3499999999999</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.273</v>
+        <v>1.222</v>
       </c>
       <c r="G3">
-        <v>0.001096491228070175</v>
+        <v>-3.245273631840797</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-3.601990049751244</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-2.537313432835821</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-2.537313432835821</v>
       </c>
       <c r="K3">
-        <v>-4.67</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L3">
-        <v>-5.120614035087719</v>
+        <v>-4.288557213930348</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>23</v>
+        <v>14.9</v>
       </c>
       <c r="V3">
-        <v>0.5927835051546392</v>
+        <v>0.58203125</v>
       </c>
       <c r="W3">
-        <v>-0.8745318352059925</v>
+        <v>-0.2780645161290322</v>
       </c>
       <c r="X3">
-        <v>0.04495311878408959</v>
+        <v>0.08647790809194258</v>
       </c>
       <c r="Y3">
-        <v>-0.9194849539900821</v>
+        <v>-0.3645424242209748</v>
       </c>
       <c r="Z3">
-        <v>1.842424242424242</v>
+        <v>0.2364427714386543</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>-0.5999294200682272</v>
       </c>
       <c r="AB3">
-        <v>0.04568040693926699</v>
+        <v>0.08489956041540894</v>
       </c>
       <c r="AC3">
-        <v>-0.04568040693926699</v>
+        <v>-0.6848289804836362</v>
       </c>
       <c r="AD3">
         <v>1.25</v>
@@ -794,28 +794,37 @@
         <v>1.25</v>
       </c>
       <c r="AG3">
-        <v>-21.75</v>
+        <v>-13.65</v>
       </c>
       <c r="AH3">
-        <v>0.03121098626716605</v>
+        <v>0.04655493482309125</v>
       </c>
       <c r="AI3">
-        <v>0.03888024883359253</v>
+        <v>0.05747126436781609</v>
       </c>
       <c r="AJ3">
-        <v>-1.275659824046921</v>
+        <v>-1.142259414225941</v>
       </c>
       <c r="AK3">
-        <v>-2.377049180327869</v>
+        <v>-1.992700729927007</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AM3">
         <v>-0.037</v>
       </c>
+      <c r="AN3">
+        <v>-0.2637130801687764</v>
+      </c>
+      <c r="AO3">
+        <v>-221.7391304347826</v>
+      </c>
+      <c r="AP3">
+        <v>2.879746835443038</v>
+      </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>137.8378378378378</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +844,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-1.03</v>
+        <v>-0.895</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -859,162 +868,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.323</v>
+        <v>0.006</v>
       </c>
       <c r="V4">
-        <v>0.06152380952380952</v>
+        <v>0.001456310679611651</v>
       </c>
       <c r="W4">
-        <v>-2.182203389830509</v>
+        <v>-3.086206896551724</v>
       </c>
       <c r="X4">
-        <v>0.04632028583490679</v>
+        <v>0.08479357313815281</v>
       </c>
       <c r="Y4">
-        <v>-2.228523675665416</v>
+        <v>-3.171000469689877</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-3.259574468085107</v>
+        <v>-1.585987261146497</v>
       </c>
       <c r="AB4">
-        <v>0.04462101158945921</v>
+        <v>0.08479357313815281</v>
       </c>
       <c r="AC4">
-        <v>-3.304195479674567</v>
+        <v>-1.67078083428465</v>
       </c>
       <c r="AD4">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.181</v>
+        <v>-0.006</v>
       </c>
       <c r="AH4">
-        <v>0.08759124087591241</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.6347607052896725</v>
+        <v>-0</v>
       </c>
       <c r="AJ4">
-        <v>0.03332719572822684</v>
+        <v>-0.001458434613514827</v>
       </c>
       <c r="AK4">
-        <v>0.3842887473460722</v>
+        <v>0.6</v>
       </c>
       <c r="AL4">
-        <v>0.067</v>
+        <v>0.058</v>
       </c>
       <c r="AM4">
-        <v>0.067</v>
+        <v>0.057</v>
       </c>
       <c r="AN4">
-        <v>-0.6622864651773982</v>
+        <v>-0</v>
       </c>
       <c r="AO4">
-        <v>-11.43283582089552</v>
+        <v>-12.87931034482759</v>
       </c>
       <c r="AP4">
-        <v>-0.2378449408672799</v>
+        <v>0.00801068090787717</v>
       </c>
       <c r="AQ4">
-        <v>-11.43283582089552</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Poda Holdings, Inc. (CNSX:PODA)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tobacco</t>
-        </is>
-      </c>
-      <c r="K5">
-        <v>-3.05</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>12.2</v>
-      </c>
-      <c r="V5">
-        <v>0.7093023255813954</v>
-      </c>
-      <c r="X5">
-        <v>0.04466634059098831</v>
-      </c>
-      <c r="AB5">
-        <v>0.04426192286414898</v>
-      </c>
-      <c r="AD5">
-        <v>0.324</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0.324</v>
-      </c>
-      <c r="AG5">
-        <v>-11.876</v>
-      </c>
-      <c r="AH5">
-        <v>0.01848892946815795</v>
-      </c>
-      <c r="AI5">
-        <v>0.02506963788300836</v>
-      </c>
-      <c r="AJ5">
-        <v>-2.230653643876785</v>
-      </c>
-      <c r="AK5">
-        <v>-16.40331491712707</v>
-      </c>
-      <c r="AL5">
-        <v>0.006</v>
-      </c>
-      <c r="AM5">
-        <v>0.006</v>
-      </c>
-      <c r="AO5">
-        <v>-508.3333333333333</v>
-      </c>
-      <c r="AQ5">
-        <v>-508.3333333333333</v>
+        <v>-13.10526315789474</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_tobacco.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_tobacco.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.222</v>
+        <v>1.595</v>
       </c>
       <c r="G2">
-        <v>-3.66268656716418</v>
+        <v>-1.058857808857809</v>
       </c>
       <c r="H2">
-        <v>-4.008955223880597</v>
+        <v>-1.08479020979021</v>
       </c>
       <c r="I2">
-        <v>-2.908955223880597</v>
+        <v>-1.280885780885781</v>
       </c>
       <c r="J2">
-        <v>-2.908955223880597</v>
+        <v>-1.280885780885781</v>
       </c>
       <c r="K2">
-        <v>-9.514999999999999</v>
+        <v>-4.469</v>
       </c>
       <c r="L2">
-        <v>-4.733830845771144</v>
+        <v>-1.302156177156177</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0005078485687903971</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.002461400760796598</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.011</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>14.906</v>
+        <v>12.137</v>
       </c>
       <c r="V2">
-        <v>0.5015477792732167</v>
+        <v>0.5603416435826409</v>
       </c>
       <c r="W2">
-        <v>-1.682135706340378</v>
+        <v>43.52199999999999</v>
       </c>
       <c r="X2">
-        <v>0.0856357406150477</v>
+        <v>0.06511368839032593</v>
       </c>
       <c r="Y2">
-        <v>-1.767771446955426</v>
+        <v>43.45688631160967</v>
       </c>
       <c r="Z2">
-        <v>0.2240303165403477</v>
-      </c>
-      <c r="AA2">
-        <v>-1.092958340607362</v>
+        <v>0.6123104371097235</v>
       </c>
       <c r="AB2">
-        <v>0.08484656677678087</v>
-      </c>
-      <c r="AC2">
-        <v>-1.177804907384143</v>
+        <v>0.06422458746043438</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG2">
-        <v>-13.656</v>
+        <v>-10.847</v>
       </c>
       <c r="AH2">
-        <v>0.04036164029706167</v>
+        <v>0.0562091503267974</v>
       </c>
       <c r="AI2">
-        <v>0.05748183573990619</v>
+        <v>0.06650512965922566</v>
       </c>
       <c r="AJ2">
-        <v>-0.8500996015936255</v>
+        <v>-1.003144363266439</v>
       </c>
       <c r="AK2">
-        <v>-1.996491228070176</v>
+        <v>-1.494077134986227</v>
       </c>
       <c r="AL2">
-        <v>0.081</v>
+        <v>0.113</v>
       </c>
       <c r="AM2">
-        <v>0.02</v>
+        <v>-0.199</v>
       </c>
       <c r="AN2">
-        <v>-0.2277281836400073</v>
+        <v>-0.3204968944099379</v>
       </c>
       <c r="AO2">
-        <v>-72.18518518518518</v>
+        <v>-38.90265486725664</v>
       </c>
       <c r="AP2">
-        <v>2.487884860630352</v>
+        <v>2.694906832298137</v>
       </c>
       <c r="AQ2">
-        <v>-292.3499999999999</v>
+        <v>22.09045226130653</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +713,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.222</v>
+        <v>1.595</v>
       </c>
       <c r="G3">
-        <v>-3.245273631840797</v>
+        <v>-0.9416422287390028</v>
       </c>
       <c r="H3">
-        <v>-3.601990049751244</v>
+        <v>-0.9677419354838709</v>
       </c>
       <c r="I3">
-        <v>-2.537313432835821</v>
+        <v>-1.18475073313783</v>
       </c>
       <c r="J3">
-        <v>-2.537313432835821</v>
+        <v>-1.18475073313783</v>
       </c>
       <c r="K3">
-        <v>-8.619999999999999</v>
+        <v>-4.12</v>
       </c>
       <c r="L3">
-        <v>-4.288557213930348</v>
+        <v>-1.208211143695015</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.011</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0006145251396648044</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.002669902912621359</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +752,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.011</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>14.9</v>
+        <v>12.1</v>
       </c>
       <c r="V3">
-        <v>0.58203125</v>
+        <v>0.6759776536312849</v>
       </c>
       <c r="W3">
-        <v>-0.2780645161290322</v>
+        <v>-0.206</v>
       </c>
       <c r="X3">
-        <v>0.08647790809194258</v>
+        <v>0.06579261572809089</v>
       </c>
       <c r="Y3">
-        <v>-0.3645424242209748</v>
+        <v>-0.2717926157280909</v>
       </c>
       <c r="Z3">
-        <v>0.2364427714386543</v>
+        <v>0.608385370205174</v>
       </c>
       <c r="AA3">
-        <v>-0.5999294200682272</v>
+        <v>-0.7207850133809099</v>
       </c>
       <c r="AB3">
-        <v>0.08489956041540894</v>
+        <v>0.06401441386830781</v>
       </c>
       <c r="AC3">
-        <v>-0.6848289804836362</v>
+        <v>-0.7847994272492178</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG3">
-        <v>-13.65</v>
+        <v>-10.81</v>
       </c>
       <c r="AH3">
-        <v>0.04655493482309125</v>
+        <v>0.0672225117248567</v>
       </c>
       <c r="AI3">
-        <v>0.05747126436781609</v>
+        <v>0.06618778860954336</v>
       </c>
       <c r="AJ3">
-        <v>-1.142259414225941</v>
+        <v>-1.524682651622003</v>
       </c>
       <c r="AK3">
-        <v>-1.992700729927007</v>
+        <v>-1.462787550744249</v>
       </c>
       <c r="AL3">
-        <v>0.023</v>
+        <v>0.112</v>
       </c>
       <c r="AM3">
-        <v>-0.037</v>
+        <v>-0.199</v>
       </c>
       <c r="AN3">
-        <v>-0.2637130801687764</v>
+        <v>-0.3514986376021799</v>
       </c>
       <c r="AO3">
-        <v>-221.7391304347826</v>
+        <v>-36.07142857142857</v>
       </c>
       <c r="AP3">
-        <v>2.879746835443038</v>
+        <v>2.94550408719346</v>
       </c>
       <c r="AQ3">
-        <v>137.8378378378378</v>
+        <v>20.30150753768844</v>
       </c>
     </row>
     <row r="4">
@@ -843,8 +843,23 @@
           <t>Tobacco</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-19.22727272727273</v>
+      </c>
+      <c r="H4">
+        <v>-19.22727272727273</v>
+      </c>
+      <c r="I4">
+        <v>-16.18181818181818</v>
+      </c>
+      <c r="J4">
+        <v>-16.18181818181818</v>
+      </c>
       <c r="K4">
-        <v>-0.895</v>
+        <v>-0.349</v>
+      </c>
+      <c r="L4">
+        <v>-15.86363636363636</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,31 +883,22 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="V4">
-        <v>0.001456310679611651</v>
+        <v>0.009840425531914894</v>
       </c>
       <c r="W4">
-        <v>-3.086206896551724</v>
+        <v>87.24999999999999</v>
       </c>
       <c r="X4">
-        <v>0.08479357313815281</v>
+        <v>0.06443476105256096</v>
       </c>
       <c r="Y4">
-        <v>-3.171000469689877</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>-1.585987261146497</v>
+        <v>87.18556523894742</v>
       </c>
       <c r="AB4">
-        <v>0.08479357313815281</v>
-      </c>
-      <c r="AC4">
-        <v>-1.67078083428465</v>
+        <v>0.06443476105256096</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -904,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.006</v>
+        <v>-0.037</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -913,28 +919,25 @@
         <v>-0</v>
       </c>
       <c r="AJ4">
-        <v>-0.001458434613514827</v>
+        <v>-0.0099382218640881</v>
       </c>
       <c r="AK4">
-        <v>0.6</v>
+        <v>0.2846153846153846</v>
       </c>
       <c r="AL4">
-        <v>0.058</v>
+        <v>0.001</v>
       </c>
       <c r="AM4">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <v>-0</v>
       </c>
       <c r="AO4">
-        <v>-12.87931034482759</v>
+        <v>-356</v>
       </c>
       <c r="AP4">
-        <v>0.00801068090787717</v>
-      </c>
-      <c r="AQ4">
-        <v>-13.10526315789474</v>
+        <v>0.1042253521126761</v>
       </c>
     </row>
   </sheetData>
